--- a/products/pack3-finance-cheat-sheets/color-of-money-decision-tree.xlsx
+++ b/products/pack3-finance-cheat-sheets/color-of-money-decision-tree.xlsx
@@ -942,6 +942,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="27.75" customHeight="1" s="50">
       <c r="B4" s="56" t="inlineStr">
         <is>
@@ -949,6 +950,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="24" customHeight="1" s="50">
       <c r="B6" s="57" t="n"/>
       <c r="C6" s="57" t="inlineStr">
@@ -1197,6 +1199,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="19.5" customHeight="1" s="50">
       <c r="B13" s="84" t="inlineStr">
         <is>
@@ -1420,10 +1423,11 @@
       </c>
       <c r="J21" s="58" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23" ht="19.5" customHeight="1" s="50">
       <c r="B23" s="89" t="inlineStr">
         <is>
-          <t>★ KEY THRESHOLD: Equipment/systems &gt;$350K unit cost = Procurement. ≤$350K = consider O&amp;M. (SAT updated to $350K per FAC 2025-07, effective Oct 1, 2025) Splitting requirements to stay under threshold is an ADA violation!</t>
+          <t>★ KEY THRESHOLD: Equipment/systems &gt;$350K unit cost = Procurement. ≤$350K = consider O&amp;M. (SAT updated to $350K per FAC 2025-06, effective Oct 1, 2025) Splitting requirements to stay under threshold is an ADA violation!</t>
         </is>
       </c>
     </row>
@@ -1534,6 +1538,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="27.75" customHeight="1" s="50">
       <c r="B4" s="57" t="inlineStr">
         <is>
@@ -2056,9 +2061,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>★ KEY THRESHOLDS (FAC 2025-07, eff. Oct 1, 2025): SAT (Simplified Acquisition Threshold) = $350,000 (increased from $250,000)  |  MPT (Micro-Purchase Threshold) = $15,000 (increased from $10,000)  |  MILCON Minor Construction = $1.5M (unspecified) / $6M (authorized)</t>
+      <c r="B18" s="49" t="inlineStr">
+        <is>
+          <t>★ KEY THRESHOLDS (FAC 2025-06, eff. Oct 1, 2025): SAT (Simplified Acquisition Threshold) = $350,000 (increased from $250,000)  |  MPT (Micro-Purchase Threshold) = $15,000 (increased from $10,000)  |  MILCON Minor Construction = $1.5M (unspecified) / $6M (authorized)</t>
         </is>
       </c>
     </row>
